--- a/assets/templates/cnss_hire_reg.xlsx
+++ b/assets/templates/cnss_hire_reg.xlsx
@@ -23,7 +23,7 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -37,7 +37,7 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="10"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -45,30 +45,14 @@
       <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
-      <sz val="14"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="13"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="16"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -91,7 +75,23 @@
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="14"/>
+      <sz val="12"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -278,7 +278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" readingOrder="2"/>
@@ -516,6 +516,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -960,12 +983,12 @@
       <c r="U2" s="2" t="n"/>
     </row>
     <row r="3" ht="21" customHeight="1">
-      <c r="A3" s="80" t="inlineStr">
+      <c r="A3" s="85" t="inlineStr">
         <is>
           <t>اعـــــــــــــلام</t>
         </is>
       </c>
-      <c r="O3" s="81" t="n"/>
+      <c r="O3" s="86" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
       <c r="R3" s="2" t="n"/>
@@ -974,12 +997,12 @@
       <c r="U3" s="2" t="n"/>
     </row>
     <row r="4" ht="21" customHeight="1">
-      <c r="A4" s="80" t="inlineStr">
+      <c r="A4" s="85" t="inlineStr">
         <is>
           <t>عن استخدام اجير</t>
         </is>
       </c>
-      <c r="O4" s="81" t="n"/>
+      <c r="O4" s="86" t="n"/>
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n"/>
@@ -1021,7 +1044,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
-      <c r="C6" s="54" t="n"/>
+      <c r="C6" s="47" t="n"/>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
@@ -1029,9 +1052,9 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
-      <c r="K6" s="64" t="n"/>
-      <c r="M6" s="64" t="n"/>
-      <c r="N6" s="64" t="n"/>
+      <c r="K6" s="87" t="n"/>
+      <c r="M6" s="87" t="n"/>
+      <c r="N6" s="87" t="n"/>
       <c r="O6" s="11" t="n"/>
       <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="n"/>
@@ -1055,10 +1078,10 @@
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="2" t="n"/>
-      <c r="K7" s="75" t="n"/>
-      <c r="L7" s="82" t="n"/>
-      <c r="M7" s="75" t="n"/>
-      <c r="N7" s="75" t="n"/>
+      <c r="K7" s="48" t="n"/>
+      <c r="L7" s="88" t="n"/>
+      <c r="M7" s="48" t="n"/>
+      <c r="N7" s="48" t="n"/>
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="2" t="n"/>
       <c r="Q7" s="2" t="n"/>
@@ -1082,9 +1105,9 @@
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="2" t="n"/>
-      <c r="K8" s="76" t="n"/>
-      <c r="L8" s="83" t="n"/>
-      <c r="M8" s="53" t="n"/>
+      <c r="K8" s="89" t="n"/>
+      <c r="L8" s="90" t="n"/>
+      <c r="M8" s="91" t="n"/>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="11" t="n"/>
       <c r="P8" s="2" t="n"/>
@@ -1163,10 +1186,10 @@
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="n"/>
-      <c r="K11" s="75" t="n"/>
-      <c r="L11" s="84" t="n"/>
-      <c r="M11" s="82" t="n"/>
-      <c r="N11" s="75" t="n"/>
+      <c r="K11" s="48" t="n"/>
+      <c r="L11" s="92" t="n"/>
+      <c r="M11" s="88" t="n"/>
+      <c r="N11" s="48" t="n"/>
       <c r="O11" s="11" t="n"/>
       <c r="P11" s="2" t="n"/>
       <c r="Q11" s="2" t="n"/>
@@ -1186,7 +1209,7 @@
           <t>ذكر</t>
         </is>
       </c>
-      <c r="C12" s="63" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1224,14 +1247,14 @@
           <t>الاسم:</t>
         </is>
       </c>
-      <c r="B13" s="54" t="n"/>
+      <c r="B13" s="47" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> الشهرة:.</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
-      <c r="E13" s="64" t="n"/>
+      <c r="E13" s="87" t="n"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> رقمه في الصندوق</t>
@@ -1240,10 +1263,10 @@
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
-      <c r="K13" s="75" t="n"/>
-      <c r="L13" s="84" t="n"/>
-      <c r="M13" s="82" t="n"/>
-      <c r="N13" s="75" t="n"/>
+      <c r="K13" s="48" t="n"/>
+      <c r="L13" s="92" t="n"/>
+      <c r="M13" s="88" t="n"/>
+      <c r="N13" s="48" t="n"/>
       <c r="O13" s="11" t="n"/>
       <c r="P13" s="2" t="n"/>
       <c r="Q13" s="2" t="n"/>
@@ -1258,7 +1281,7 @@
           <t>اسم الاب :</t>
         </is>
       </c>
-      <c r="B14" s="64" t="n"/>
+      <c r="B14" s="87" t="n"/>
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -1267,7 +1290,7 @@
       </c>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
-      <c r="H14" s="64" t="n"/>
+      <c r="H14" s="87" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
@@ -1287,24 +1310,24 @@
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
-      <c r="C15" s="54" t="n"/>
-      <c r="D15" s="54" t="n"/>
-      <c r="E15" s="60" t="n"/>
+      <c r="C15" s="47" t="n"/>
+      <c r="D15" s="47" t="n"/>
+      <c r="E15" s="93" t="n"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>رقم السجل:</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
-      <c r="H15" s="54" t="n"/>
-      <c r="I15" s="60" t="n"/>
+      <c r="H15" s="47" t="n"/>
+      <c r="I15" s="93" t="n"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> الجنسية:</t>
         </is>
       </c>
       <c r="K15" s="2" t="n"/>
-      <c r="L15" s="64" t="n"/>
+      <c r="L15" s="87" t="n"/>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="11" t="n"/>
       <c r="P15" s="2" t="n"/>
@@ -1325,7 +1348,7 @@
           <t>اعزب</t>
         </is>
       </c>
-      <c r="C16" s="75" t="inlineStr">
+      <c r="C16" s="48" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1335,7 +1358,7 @@
           <t>متأهل</t>
         </is>
       </c>
-      <c r="E16" s="75" t="inlineStr">
+      <c r="E16" s="48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1387,10 +1410,10 @@
           <t>استخدم فيها منذ:</t>
         </is>
       </c>
-      <c r="B17" s="64" t="n"/>
-      <c r="C17" s="54" t="n"/>
-      <c r="D17" s="54" t="n"/>
-      <c r="E17" s="54" t="n"/>
+      <c r="B17" s="87" t="n"/>
+      <c r="C17" s="47" t="n"/>
+      <c r="D17" s="47" t="n"/>
+      <c r="E17" s="47" t="n"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>عدد ساعات العمل في الشهر</t>
@@ -1399,7 +1422,7 @@
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
-      <c r="J17" s="54" t="n"/>
+      <c r="J17" s="47" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
@@ -1418,7 +1441,7 @@
           <t>بدوام كامل</t>
         </is>
       </c>
-      <c r="B18" s="75" t="inlineStr">
+      <c r="B18" s="48" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1458,21 +1481,21 @@
         </is>
       </c>
       <c r="B19" s="2" t="n"/>
-      <c r="C19" s="62" t="n"/>
-      <c r="D19" s="62" t="n"/>
+      <c r="C19" s="94" t="n"/>
+      <c r="D19" s="94" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ان الراتب الحالي </t>
         </is>
       </c>
-      <c r="G19" s="54" t="n"/>
+      <c r="G19" s="47" t="n"/>
       <c r="H19" s="2" t="n"/>
-      <c r="J19" s="54" t="n"/>
-      <c r="K19" s="54" t="n"/>
-      <c r="L19" s="54" t="n"/>
-      <c r="M19" s="54" t="n"/>
-      <c r="N19" s="54" t="n"/>
-      <c r="O19" s="61" t="n"/>
+      <c r="J19" s="47" t="n"/>
+      <c r="K19" s="47" t="n"/>
+      <c r="L19" s="47" t="n"/>
+      <c r="M19" s="47" t="n"/>
+      <c r="N19" s="47" t="n"/>
+      <c r="O19" s="95" t="n"/>
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
       <c r="R19" s="2" t="n"/>
@@ -1487,7 +1510,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
-      <c r="C20" s="75" t="inlineStr">
+      <c r="C20" s="48" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1718,8 +1741,8 @@
           <t>اسم الاجير                                       التوقيع</t>
         </is>
       </c>
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
+      <c r="B27" s="47" t="n"/>
+      <c r="C27" s="47" t="n"/>
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n"/>
@@ -1728,7 +1751,7 @@
       <c r="I27" s="2" t="n"/>
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="n"/>
-      <c r="L27" s="54" t="n"/>
+      <c r="L27" s="47" t="n"/>
       <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="11" t="n"/>

--- a/assets/templates/cnss_hire_reg.xlsx
+++ b/assets/templates/cnss_hire_reg.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="اعلام استخدام اجير" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'اعلام استخدام اجير'!$A$1:$U$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'اعلام استخدام اجير'!$A$1:$O$38</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -276,9 +276,9 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" readingOrder="2"/>
@@ -538,6 +538,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -988,7 +991,7 @@
           <t>اعـــــــــــــلام</t>
         </is>
       </c>
-      <c r="O3" s="86" t="n"/>
+      <c r="O3" s="81" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
       <c r="R3" s="2" t="n"/>
@@ -1002,7 +1005,7 @@
           <t>عن استخدام اجير</t>
         </is>
       </c>
-      <c r="O4" s="86" t="n"/>
+      <c r="O4" s="81" t="n"/>
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n"/>
@@ -1079,7 +1082,7 @@
       <c r="I7" s="2" t="n"/>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="48" t="n"/>
-      <c r="L7" s="88" t="n"/>
+      <c r="L7" s="82" t="n"/>
       <c r="M7" s="48" t="n"/>
       <c r="N7" s="48" t="n"/>
       <c r="O7" s="11" t="n"/>
@@ -1106,7 +1109,7 @@
       <c r="I8" s="2" t="n"/>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="89" t="n"/>
-      <c r="L8" s="90" t="n"/>
+      <c r="L8" s="83" t="n"/>
       <c r="M8" s="91" t="n"/>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="11" t="n"/>
@@ -1187,8 +1190,8 @@
       <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="48" t="n"/>
-      <c r="L11" s="92" t="n"/>
-      <c r="M11" s="88" t="n"/>
+      <c r="L11" s="84" t="n"/>
+      <c r="M11" s="82" t="n"/>
       <c r="N11" s="48" t="n"/>
       <c r="O11" s="11" t="n"/>
       <c r="P11" s="2" t="n"/>
@@ -1264,8 +1267,8 @@
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="48" t="n"/>
-      <c r="L13" s="92" t="n"/>
-      <c r="M13" s="88" t="n"/>
+      <c r="L13" s="84" t="n"/>
+      <c r="M13" s="82" t="n"/>
       <c r="N13" s="48" t="n"/>
       <c r="O13" s="11" t="n"/>
       <c r="P13" s="2" t="n"/>
@@ -1474,7 +1477,7 @@
       <c r="T18" s="2" t="n"/>
       <c r="U18" s="2" t="n"/>
     </row>
-    <row r="19" ht="21.9" customHeight="1">
+    <row r="19" ht="44" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
           <t>* عمل الأجير الحالي:</t>
@@ -1488,14 +1491,8 @@
           <t xml:space="preserve">ان الراتب الحالي </t>
         </is>
       </c>
-      <c r="G19" s="47" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="J19" s="47" t="n"/>
-      <c r="K19" s="47" t="n"/>
-      <c r="L19" s="47" t="n"/>
-      <c r="M19" s="47" t="n"/>
-      <c r="N19" s="47" t="n"/>
-      <c r="O19" s="95" t="n"/>
+      <c r="G19" s="96" t="n"/>
+      <c r="O19" s="81" t="n"/>
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
       <c r="R19" s="2" t="n"/>
@@ -2060,11 +2057,12 @@
       <c r="U38" s="2" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="K13:M13"/>
+    <mergeCell ref="G19:O19"/>
     <mergeCell ref="L15:M15"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="E13:F13"/>
@@ -2073,7 +2071,7 @@
     <mergeCell ref="A4:O4"/>
     <mergeCell ref="A3:O3"/>
   </mergeCells>
-  <printOptions horizontalCentered="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.5" bottom="0" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>

--- a/assets/templates/cnss_hire_reg.xlsx
+++ b/assets/templates/cnss_hire_reg.xlsx
@@ -931,7 +931,7 @@
     <col width="9.109375" customWidth="1" style="17" min="19" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1">
+    <row r="1" ht="21.3" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
           <t>الصندوق الوطني</t>
@@ -958,7 +958,7 @@
       <c r="T1" s="2" t="n"/>
       <c r="U1" s="2" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="16.5" customHeight="1">
       <c r="A2" s="43" t="inlineStr">
         <is>
           <t>للضمان الاجتماعي</t>
@@ -985,7 +985,7 @@
       <c r="T2" s="2" t="n"/>
       <c r="U2" s="2" t="n"/>
     </row>
-    <row r="3" ht="21" customHeight="1">
+    <row r="3" ht="22.3" customHeight="1">
       <c r="A3" s="85" t="inlineStr">
         <is>
           <t>اعـــــــــــــلام</t>
@@ -999,7 +999,7 @@
       <c r="T3" s="2" t="n"/>
       <c r="U3" s="2" t="n"/>
     </row>
-    <row r="4" ht="21" customHeight="1">
+    <row r="4" ht="22.3" customHeight="1">
       <c r="A4" s="85" t="inlineStr">
         <is>
           <t>عن استخدام اجير</t>
@@ -1013,7 +1013,7 @@
       <c r="T4" s="2" t="n"/>
       <c r="U4" s="2" t="n"/>
     </row>
-    <row r="5" ht="21.9" customHeight="1">
+    <row r="5" ht="23.2" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>ان صاحب العمل الموقع ادناه</t>
@@ -1040,7 +1040,7 @@
       <c r="T5" s="2" t="n"/>
       <c r="U5" s="2" t="n"/>
     </row>
-    <row r="6" ht="21.9" customHeight="1">
+    <row r="6" ht="23.2" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>المسؤول عن مؤسسة</t>
@@ -1066,7 +1066,7 @@
       <c r="T6" s="2" t="n"/>
       <c r="U6" s="2" t="n"/>
     </row>
-    <row r="7" ht="21.9" customHeight="1">
+    <row r="7" ht="23.2" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>المسجلة في الصندوق الوطني للضمان الاجتماعي تحت رقم:</t>
@@ -1093,7 +1093,7 @@
       <c r="T7" s="2" t="n"/>
       <c r="U7" s="2" t="n"/>
     </row>
-    <row r="8" ht="21.9" customHeight="1">
+    <row r="8" ht="23.2" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>سجل تجاري: مكان........................................ رقم........................................... هاتف</t>
@@ -1120,7 +1120,7 @@
       <c r="T8" s="2" t="n"/>
       <c r="U8" s="2" t="n"/>
     </row>
-    <row r="9" ht="21.9" customHeight="1">
+    <row r="9" ht="23.2" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">وعنوانها الكامل:  </t>
@@ -1147,7 +1147,7 @@
       <c r="T9" s="2" t="n"/>
       <c r="U9" s="2" t="n"/>
     </row>
-    <row r="10" ht="21.9" customHeight="1">
+    <row r="10" ht="23.2" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>...............................................................................................................................................</t>
@@ -1174,7 +1174,7 @@
       <c r="T10" s="2" t="n"/>
       <c r="U10" s="2" t="n"/>
     </row>
-    <row r="11" ht="21.9" customHeight="1">
+    <row r="11" ht="23.2" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>يصرح بأن الأجير المبينةهويته فيما يلي والمسجل في الصندوق تحت الرقم</t>
@@ -1201,7 +1201,7 @@
       <c r="T11" s="2" t="n"/>
       <c r="U11" s="2" t="n"/>
     </row>
-    <row r="12" ht="21.9" customHeight="1">
+    <row r="12" ht="23.2" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
           <t>الجنس:</t>
@@ -1244,7 +1244,7 @@
       <c r="T12" s="2" t="n"/>
       <c r="U12" s="2" t="n"/>
     </row>
-    <row r="13" ht="21.9" customHeight="1">
+    <row r="13" ht="23.2" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>الاسم:</t>
@@ -1278,7 +1278,7 @@
       <c r="T13" s="2" t="n"/>
       <c r="U13" s="2" t="n"/>
     </row>
-    <row r="14" ht="21.9" customHeight="1">
+    <row r="14" ht="23.2" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>اسم الاب :</t>
@@ -1306,7 +1306,7 @@
       <c r="T14" s="2" t="n"/>
       <c r="U14" s="2" t="n"/>
     </row>
-    <row r="15" ht="21.9" customHeight="1">
+    <row r="15" ht="23.2" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>تاريخ ومحل الولادة:</t>
@@ -1340,7 +1340,7 @@
       <c r="T15" s="2" t="n"/>
       <c r="U15" s="2" t="n"/>
     </row>
-    <row r="16" ht="21.9" customHeight="1">
+    <row r="16" ht="23.2" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>الوضع العائلي:</t>
@@ -1407,7 +1407,7 @@
       <c r="T16" s="2" t="n"/>
       <c r="U16" s="2" t="n"/>
     </row>
-    <row r="17" ht="21.9" customHeight="1">
+    <row r="17" ht="23.2" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>استخدم فيها منذ:</t>
@@ -1438,7 +1438,7 @@
       <c r="T17" s="2" t="n"/>
       <c r="U17" s="2" t="n"/>
     </row>
-    <row r="18" ht="21.9" customHeight="1">
+    <row r="18" ht="23.2" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
           <t>بدوام كامل</t>
@@ -1477,7 +1477,7 @@
       <c r="T18" s="2" t="n"/>
       <c r="U18" s="2" t="n"/>
     </row>
-    <row r="19" ht="44" customHeight="1">
+    <row r="19" ht="46.6" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
           <t>* عمل الأجير الحالي:</t>
@@ -1500,7 +1500,7 @@
       <c r="T19" s="2" t="n"/>
       <c r="U19" s="2" t="n"/>
     </row>
-    <row r="20" ht="21.9" customHeight="1">
+    <row r="20" ht="23.2" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
           <t>* طريقة دفع الأجر:</t>
@@ -1558,7 +1558,7 @@
       <c r="T20" s="2" t="n"/>
       <c r="U20" s="2" t="n"/>
     </row>
-    <row r="21" ht="21.9" customHeight="1">
+    <row r="21" ht="23.2" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
           <t>* هل يعمل حسب معرفتك لدى صاحب عمل آخر:</t>
@@ -1601,7 +1601,7 @@
       <c r="T21" s="2" t="n"/>
       <c r="U21" s="2" t="n"/>
     </row>
-    <row r="22" ht="21.9" customHeight="1">
+    <row r="22" ht="23.2" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
           <t>................................................................................................</t>
@@ -1628,7 +1628,7 @@
       <c r="T22" s="2" t="n"/>
       <c r="U22" s="2" t="n"/>
     </row>
-    <row r="23" ht="21.9" customHeight="1">
+    <row r="23" ht="23.2" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
           <t>* اسم وعنوان صاحب العمل الذي كان الاجير يعمل لديه قبل دخوله مؤسستي:...................................................</t>
@@ -1655,7 +1655,7 @@
       <c r="T23" s="2" t="n"/>
       <c r="U23" s="2" t="n"/>
     </row>
-    <row r="24" ht="21.9" customHeight="1">
+    <row r="24" ht="23.2" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>................................................................................................ رقمه في الصندوق</t>
@@ -1682,7 +1682,7 @@
       <c r="T24" s="2" t="n"/>
       <c r="U24" s="2" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="16.5" customHeight="1">
       <c r="A25" s="18" t="n"/>
       <c r="B25" s="19" t="n"/>
       <c r="C25" s="19" t="n"/>
@@ -1705,7 +1705,7 @@
       <c r="T25" s="2" t="n"/>
       <c r="U25" s="2" t="n"/>
     </row>
-    <row r="26" ht="17.1" customHeight="1">
+    <row r="26" ht="18.1" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
           <t>* أوافق على صحة المعلومات المدرجة أعلاه:                                       ختم المؤسسة                     اسم وتوقيع الشخص المسؤؤول</t>
@@ -1732,7 +1732,7 @@
       <c r="T26" s="2" t="n"/>
       <c r="U26" s="2" t="n"/>
     </row>
-    <row r="27" ht="25.05" customHeight="1">
+    <row r="27" ht="26.6" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
         <is>
           <t>اسم الاجير                                       التوقيع</t>
@@ -1759,7 +1759,7 @@
       <c r="T27" s="2" t="n"/>
       <c r="U27" s="2" t="n"/>
     </row>
-    <row r="28" ht="65.09999999999999" customHeight="1">
+    <row r="28" ht="69" customHeight="1">
       <c r="A28" s="10" t="n"/>
       <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="n"/>
@@ -1782,7 +1782,7 @@
       <c r="T28" s="2" t="n"/>
       <c r="U28" s="2" t="n"/>
     </row>
-    <row r="29" ht="17.1" customHeight="1">
+    <row r="29" ht="18.1" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
         <is>
           <t>....................... في ..................200                                                             .................. في ...................200</t>
@@ -1809,7 +1809,7 @@
       <c r="T29" s="2" t="n"/>
       <c r="U29" s="2" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="16.5" customHeight="1">
       <c r="A30" s="16" t="n"/>
       <c r="B30" s="8" t="n"/>
       <c r="C30" s="8" t="n"/>
@@ -1832,7 +1832,7 @@
       <c r="T30" s="2" t="n"/>
       <c r="U30" s="2" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="16.5" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
         <is>
           <t>حقل مخصص للصندوق:</t>
@@ -1863,7 +1863,7 @@
       <c r="T31" s="2" t="n"/>
       <c r="U31" s="2" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="16.5" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
           <t>عولج في مركز:..........................................</t>
@@ -1894,7 +1894,7 @@
       <c r="T32" s="2" t="n"/>
       <c r="U32" s="2" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="16.5" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
           <t>بتاريخ........................ في.......................200</t>
@@ -1921,7 +1921,7 @@
       <c r="T33" s="2" t="n"/>
       <c r="U33" s="2" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="16.5" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
           <t>اسم وتوقيع المستخدم</t>
@@ -1952,7 +1952,7 @@
       <c r="T34" s="2" t="n"/>
       <c r="U34" s="2" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="16.5" customHeight="1">
       <c r="A35" s="18" t="n"/>
       <c r="B35" s="19" t="n"/>
       <c r="C35" s="19" t="n"/>
@@ -1975,7 +1975,7 @@
       <c r="T35" s="2" t="n"/>
       <c r="U35" s="2" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="16.5" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
         <is>
           <t>* تملأ هذه المطبوعة وترسل الى الصندوق الوطني للضمان الاجتماعي كلما استخدمت المؤسسة اجيرا جديدا سبق أن جرى تسجيل</t>
@@ -2002,7 +2002,7 @@
       <c r="T36" s="2" t="n"/>
       <c r="U36" s="2" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="16.5" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
           <t>في الصندوق وذلك ضمن مهلة 15 يوما من تاريخ الاستخدام</t>
@@ -2029,7 +2029,7 @@
       <c r="T37" s="2" t="n"/>
       <c r="U37" s="2" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" ht="16.5" customHeight="1">
       <c r="A38" s="18" t="inlineStr">
         <is>
           <t>* تنبيه: يهمل كل أعلام غير مرفق باخراج قيد فردي للعازب وعائلي للمتأهل وغير مكتوب بخط واضح ومقروء، واذا كانت المعلومات ناقصة.</t>

--- a/assets/templates/cnss_hire_reg.xlsx
+++ b/assets/templates/cnss_hire_reg.xlsx
@@ -278,7 +278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" readingOrder="2"/>
@@ -541,6 +541,21 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1478,21 +1493,29 @@
       <c r="U18" s="2" t="n"/>
     </row>
     <row r="19" ht="46.6" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="97" t="inlineStr">
         <is>
           <t>* عمل الأجير الحالي:</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="94" t="n"/>
-      <c r="D19" s="94" t="n"/>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="B19" s="98" t="n"/>
+      <c r="C19" s="99" t="n"/>
+      <c r="D19" s="99" t="n"/>
+      <c r="E19" s="98" t="inlineStr">
         <is>
           <t xml:space="preserve">ان الراتب الحالي </t>
         </is>
       </c>
+      <c r="F19" s="100" t="n"/>
       <c r="G19" s="96" t="n"/>
-      <c r="O19" s="81" t="n"/>
+      <c r="H19" s="100" t="n"/>
+      <c r="I19" s="100" t="n"/>
+      <c r="J19" s="100" t="n"/>
+      <c r="K19" s="100" t="n"/>
+      <c r="L19" s="100" t="n"/>
+      <c r="M19" s="100" t="n"/>
+      <c r="N19" s="100" t="n"/>
+      <c r="O19" s="101" t="n"/>
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
       <c r="R19" s="2" t="n"/>
